--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_04_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_04_20_Cau.xlsx
@@ -678,7 +678,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Điểm phê duyệt phải đứng ngay trước hành động khó đảo ngược.</t>
+          <t>Luồng hoàn tiền an toàn: Tạo bản nháp từ dữ liệu đã kiểm tra (o3) -&gt; Hiển thị người nhận, số tiền, lý do và bản nháp (o2) -&gt; Người xem xét sửa/chấp thuận/từ chối (o4) -&gt; Thực thi gửi email và hoàn tiền (o1).</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thông báo phần nào hỏng, phần nào còn nguyên và người dùng có thể làm gì tiếp.</t>
+          <t>Khi retrieval lỗi nhưng dữ liệu form người dùng đã nhập còn nguyên, phản hồi an toàn: Giữ nguyên biểu mẫu và nêu rõ chưa lấy được nguồn (a), Cho phép thử lại hoặc lưu bản nháp (b), và Cho phép chuyển cho nhân viên xử lý nếu gấp (e).</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So điều kiện đang chạy với các điều kiện đã kiểm thử.</t>
+          <t>Camera chỉ được kiểm thử vào ban ngày; khi chạy ban đêm có cảm biến báo lux dưới ngưỡng nghĩa là hệ thống đang hoạt động ngoài phạm vi thiết kế vận hành (ODD). Hành động đúng là giảm chức năng hoặc bàn giao theo chính sách an toàn.</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xem xác suất và mức độ nghiêm trọng như hai trục, không loại rủi ro ở phần đuôi.</t>
+          <t>Rủi ro B tuy xác suất thấp (chưa xuất hiện trong 100 lần) nhưng mức độ nghiêm trọng cực cao (xóa dữ liệu khách hàng); Rủi ro A xảy ra thường xuyên nhưng tác động chỉ làm chậm 1 phút. Cách xử lý chuẩn là khoanh vùng/chuyển cấp xử lý ngay rủi ro B, đồng thời xử lý A theo tác động.</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đếm số điểm khác nhau giữa nhóm đối chứng và nhóm thử nghiệm.</t>
+          <t>Khi nhóm thử nghiệm đồng thời thay đổi cả tìm kiếm mới lẫn quy trình bắt đầu sử dụng (onboarding), hai biến bị thay đổi cùng lúc nên không thể cô lập và xác định được yếu tố nào là nguyên nhân chính làm tăng tỷ lệ giữ chân.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_04_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_04_20_Cau.xlsx
@@ -626,10 +626,19 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách điều bảng giá chứng minh được khỏi điều còn thiếu.
-Phân tích theo nguyên lý thiết kế: Tách điều bảng giá chứng minh được khỏi điều còn thiếu.</t>
+- Viết lại câu trả lời minh bạch (2.0 điểm): Trình bày rõ giá cơ bản của A rẻ nhất theo dữ liệu cũ, chỉ rõ giới hạn 8 tháng và việc thiếu phí hỗ trợ của B.
+- Khuyến nghị hành động kiểm chứng (1.0 điểm): Đưa ra khuyến nghị cập nhật báo giá mới trước khi quyết định, giải thích nguyên lý minh bạch dữ liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Viết lại câu trả lời với mức độ minh bạch bằng chứng chuẩn xác:
+"Theo dữ liệu bảng giá thu thập từ 8 tháng trước, Nhà cung cấp A hiện có mức giá dịch vụ cơ bản thấp nhất trong các đơn vị được khảo sát. Tuy nhiên, kết luận này có hai giới hạn quan trọng cần lưu ý:
+1. Dữ liệu đã cũ (8 tháng trước) và giá thực tế của các nhà cung cấp có thể đã thay đổi.
+2. So sánh hiện tại chưa bao gồm chi phí hỗ trợ kỹ thuật của Nhà cung cấp B do thiếu thông tin trong hồ sơ.
+Khuyến nghị: Bạn nên yêu cầu bảng báo giá cập nhật mới nhất kèm chi phí hỗ trợ trọn gói từ cả hai nhà cung cấp trước khi đưa ra quyết định lựa chọn."
+Giải thích: Câu trả lời mới tuân thủ nguyên tắc minh bạch bằng chứng: Tách biệt rõ ràng điều dữ liệu chứng minh được (giá cơ bản cũ) khỏi các điểm mù và giả định chưa kiểm chứng (thời gian trôi qua, thiếu phí hỗ trợ của B), giúp người dùng không bị đánh lừa bởi một kết luận tuyệt đối sai lệch.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc 'Epistemic Humility &amp; Evidence Transparency' trong AI: Hệ thống không được phép đưa ra các kết luận tuyệt đối mang tính phán xét ('A rẻ nhất') khi dữ liệu nền tảng bị khiếm khuyết. Công khai ranh giới tri thức giúp bảo vệ người dùng khỏi các quyết định tài chính sai lầm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Set Expectations on Limitations (https://pair.withgoogle.com/guidebook/); ISO/IEC 42001 - Artificial Intelligence Management System.</t>
         </is>
       </c>
     </row>
@@ -707,10 +716,30 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Người xem xét cần thấy chính xác điều gì sẽ thay đổi trước khi thực hiện.
-Phân tích theo nguyên lý thiết kế: Người xem xét cần thấy chính xác điều gì sẽ thay đổi trước khi thực hiện.</t>
+- Thiết kế màn hình phê duyệt đầy đủ thông tin (1.5 điểm): Trình bày tiêu chí lọc, bảng preview, nút xuất CSV và cơ chế gõ chữ xác nhận chống bấm nhầm.
+- Hành vi khi Chấp thuận (1.0 điểm): Thực hiện Soft delete an toàn kèm ghi audit log bất biến.
+- Hành vi khi Từ chối (0.5 điểm): Hủy bỏ lệnh an toàn, ghi nhận lý do từ chối.
+- Hành vi khi Chỉnh sửa (1.0 điểm): Cho phép lọc bỏ tài khoản ngoại lệ, cập nhật lại số lượng và yêu cầu xác nhận danh sách mới.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế màn hình phê duyệt hàng loạt an toàn (Bulk Approval Interface Design):
+- Tiêu đề cảnh báo rủi ro cao: 'XÁC NHẬN PHÊ DUYỆT: XÓA 1.200 TÀI KHOẢN KHÔNG HOẠT ĐỘNG'.
+- Bảng tóm tắt định lượng: Hiển thị tiêu chí lọc ('Tài khoản không đăng nhập &gt; 24 tháng, số dư = 0'), tổng số tài khoản bị ảnh hưởng (1.200).
+- Bảng dữ liệu xem trước (Preview Table): Hiển thị danh sách 50 tài khoản mẫu đầu tiên (UserID, Email ẩn danh, Ngày đăng nhập cuối) kèm nút 'Tải file CSV danh sách đầy đủ 1.200 tài khoản' để kiểm toán trước khi duyệt.
+- Cơ chế an toàn kép: Bắt buộc người phê duyệt phải gõ đúng chuỗi chữ 'XOA 1200 TAI KHOAN' vào ô xác nhận trước khi nút hành động được kích hoạt (ngăn chặn bấm nhầm vô thức).
+2. Hành vi chi tiết của hệ thống theo từng lựa chọn:
+- Khi người dùng CHẤP THUẬN (Approve):
+  + Hệ thống không xóa vật lý ngay lập tức (Hard Delete) mà chuyển trạng thái sang 'Xóa mềm / Tạm khóa' (Soft Delete) trong vòng 30 ngày để cho phép phục hồi nếu có sai sót.
+  + Ghi nhật ký kiểm toán bất biến (Audit Log) lưu rõ: AdminID, Timestamp, Tiêu chí xóa và Snapshot danh sách tài khoản.
+- Khi người dùng TỪ CHỐI (Reject):
+  + Hủy bỏ hoàn toàn tác vụ xóa trong hàng đợi; mở hộp thoại yêu cầu Admin ghi lý do từ chối để làm dữ liệu tinh chỉnh cho agent.
+  + Gửi thông báo an toàn xác nhận không có bất kỳ tài khoản nào bị thay đổi trạng thái.
+- Khi người dùng CHỈNH SỬA (Modify / Exclude):
+  + Cung cấp tính năng loại trừ (Exclusion list): Cho phép Admin lọc bỏ hoặc bỏ chọn một số tài khoản đặc biệt (ví dụ tài khoản VIP, tài khoản đối tác) ra khỏi danh sách xóa.
+  + Hệ thống cập nhật lại số lượng (ví dụ từ 1.200 xuống 1.185 tài khoản) và yêu cầu xác nhận lại trên danh sách mới.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Đối với các hành động phá hủy hàng loạt (Destructive Bulk Actions), nguyên tắc Human-Centered Safety đòi hỏi màn hình phê duyệt phải có: Bằng chứng tác động rõ ràng (Impact Transparency), Cơ chế xác nhận có ma sát chủ ý (Friction-based Confirmation), Khả năng chỉnh sửa loại trừ linh hoạt, và Cơ chế xóa mềm phục hồi được (Soft-delete Safety Net).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nielsen Norman Group - Confirmation Dialogs and Destructive Actions (https://www.nngroup.com/articles/confirmation-dialog/); Microsoft HAX Toolkit - Support Efficient Correction (https://www.microsoft.com/en-us/haxtoolkit/)</t>
         </is>
       </c>
     </row>
@@ -741,10 +770,24 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết ba nhánh theo điều kiện và người nhận việc chuyển cấp.
-Phân tích theo nguyên lý thiết kế: Viết ba nhánh theo điều kiện và người nhận việc chuyển cấp.</t>
+- Quy tắc nhánh ALLOW (1.0 điểm): Nêu rõ điều kiện dưới 2 triệu và thuộc danh mục duyệt trước để agent tự đặt hàng.
+- Quy tắc nhánh DENY (1.0 điểm): Nêu rõ điều kiện hàng cấm/không có quyền để từ chối dứt điểm.
+- Quy tắc nhánh ESCALATE (1.0 điểm): Nêu rõ điều kiện trên 2 triệu hoặc ngoài danh mục để chuyển tiếp Trưởng phòng Hành chính duyệt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Quy tắc phân quyền ranh giới tự chủ (Autonomy Scope Boundary Rules):
+1. Nhánh Cho phép (ALLOW - Autonomous Execution):
+- Điều kiện: Tổng giá trị đơn hàng &lt; 2.000.000 VNĐ VÀ 100% các mặt hàng nằm trong danh mục văn phòng phẩm đã được phê duyệt trước (Pre-approved Catalog).
+- Hành vi: Agent tự động tạo đơn mua, gọi API đặt hàng của nhà cung cấp và gửi email thông báo xác nhận đặt hàng thành công cho người yêu cầu.
+2. Nhánh Từ chối thẳng (DENY - Fast Failure):
+- Điều kiện: Đơn hàng chứa các mặt hàng nằm trong danh mục hàng hóa bị cấm (Blacklist - ví dụ thiết bị điện tử đắt tiền, đồ dùng cá nhân) HOẶC tài khoản người yêu cầu không có quyền đặt hàng.
+- Hành vi: Agent lập tức hủy yêu cầu, không gọi bất kỳ API mua hàng nào và gửi thông báo từ chối nêu rõ điều khoản chính sách vi phạm.
+3. Nhánh Chuyển cấp (ESCALATE - Human-in-the-loop Gate):
+- Điều kiện: Tổng giá trị đơn hàng &gt;= 2.000.000 VNĐ HOẶC đơn hàng chứa các mặt hàng hợp lệ nhưng chưa có trong danh mục duyệt trước (cần bổ sung danh mục).
+- Hành vi &amp; Người nhận: Agent khóa trạng thái đơn hàng ở mức 'Chờ phê duyệt', tự động đóng gói phiếu đề xuất kèm lý do và chuyển tiếp đến Trưởng phòng Hành chính / Quản lý trực tiếp qua Slack/Email để xem xét phê duyệt thủ công.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mẫu hình phân quyền 'Allow-Deny-Escalate' thiết lập hàng rào bảo vệ vững chắc cho tác nhân tự trị. Thay vì để agent tự do đưa ra quyết định ở các vùng xám, quy tắc cứng (Hard Policies) đảm bảo agent chỉ được tự hành trong phạm vi rủi ro tài chính thấp, đồng thời thiết lập lối thoát an toàn chuyển giao cho con người khi chạm ngưỡng giới hạn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Microsoft HAX Toolkit - Guideline 10: Scope of Action (https://www.microsoft.com/en-us/haxtoolkit/); OWASP Top 10 for LLMs - LLM08: Excessive Agency (https://owasp.org/www-project-top-10-for-large-language-model-applications/)</t>
         </is>
       </c>
     </row>
@@ -777,10 +820,24 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách thao tác trên mã/tệp khỏi tác động bên ngoài và secret.
-Phân tích theo nguyên lý thiết kế: Tách thao tác trên mã/tệp khỏi tác động bên ngoài và secret.</t>
+- Xác định rõ ranh giới quyền được phép và bị cấm (1.5 điểm): Nêu rõ chỉ sửa code/test trong sandbox, cấm merge, cấm secret, cấm deploy.
+- Cách xử lý yêu cầu vượt phạm vi chuẩn mực (1.5 điểm): Từ chối thẳng thắn, ghi audit log và hướng dẫn con người thực hiện quy trình thủ công an toàn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết lập ranh giới quyền hạn nghiêm ngặt (Least Privilege Boundary for Coding Agent):
+- Quyền được phép (Allowed Scope): Đọc mã nguồn, tạo nhánh phụ (feature branch), sửa đổi tệp mã nguồn cục bộ và chạy các lệnh kiểm thử tự động (unit test, linter) trong phạm vi môi trường sandbox cô lập của một kho mã duy nhất.
+- Ranh giới bị cấm (Forbidden Scope):
+  + Cấm Merge: Tuyệt đối không cấp quyền merge vào nhánh chính (main/master). Mọi thay đổi bắt buộc phải thông qua Pull Request (PR).
+  + Cấm đọc Secret: Cô lập biến môi trường nhạy cảm; agent không có quyền truy cập vào file `.env`, vault secret, hoặc private keys.
+  + Cấm Deploy: Không cấp quyền truy cập vào hạ tầng CI/CD production hoặc các lệnh phát hành máy chủ.
+2. Cách xử lý yêu cầu vượt phạm vi (Handling Out-of-Scope Requests):
+Khi người dùng yêu cầu hành động vượt quyền (ví dụ: 'Hãy merge PR này vào main' hoặc 'Đọc API key trong vault'):
+- Agent lập tức từ chối thực thi lệnh: 'Hành động này nằm ngoài phạm vi tự chủ được cấp phép của tôi.'
+- Không cố gắng chạy lách lệnh bằng terminal; ghi log cảnh báo an ninh (Audit Log) về hành vi vi phạm.
+- Hướng dẫn người dùng các bước tiếp theo: 'Vui lòng tự tạo Pull Request trên GitHub và yêu cầu Tech Lead duyệt merge thủ công theo quy trình CI/CD'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc đặc quyền tối thiểu (Principle of Least Privilege - PoLP) trong kiến trúc Agentic Coding: Tác nhân AI sinh mã chỉ được phép hoạt động trong không gian thử nghiệm (Sandbox workspace). Các hành động thay đổi trạng thái sản xuất (Merge, Deploy) hoặc truy cập bí mật bắt buộc phải được bảo vệ bởi ranh giới phân quyền hạ tầng (RBAC/IAM), không phụ thuộc vào lời hứa của prompt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Saltzer, J. H., &amp; Schroeder, M. D. (1975). The Protection of Information in Computer Systems (Principle of Least Privilege); GitHub Actions Security Hardening Guide (https://docs.github.com/en/actions/security-guides/security-hardening-for-github-actions)</t>
         </is>
       </c>
     </row>
@@ -863,10 +920,24 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng biến việc hết thời gian chờ thành kết luận; bảo vệ khỏi hành động lặp.
-Phân tích theo nguyên lý thiết kế: Đừng biến việc hết thời gian chờ thành kết luận; bảo vệ khỏi hành động lặp.</t>
+- Thông báo minh bạch, trấn an người dùng (1.0 điểm): Nhắc nhở rõ ràng không bấm thanh toán lại và nêu thời gian đang kiểm tra đối soát.
+- Thiết lập trạng thái cô lập khóa idempotency (1.5 điểm): Chuyển trạng thái đơn sang pending verification, khóa nút bấm và dùng idempotency key chống trừ tiền 2 lần.
+- Phương án phục hồi tự động 2 kịch bản (1.5 điểm): Thiết kế background polling tra cứu cổng thanh toán, xử lý dứt điểm cả kịch bản thành công và kịch bản hủy an toàn sau 5 phút.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế xử lý sự cố hết thời gian chờ (Timeout) thanh toán an toàn và phục hồi trải nghiệm:
+1. Thông báo minh bạch cho người dùng (User Message):
+"Yêu cầu thanh toán của bạn đang được cổng thanh toán xử lý nhưng phản hồi bị chậm hơn dự kiến. Xin bạn VUI LÒNG KHÔNG BẤM THANH TOÁN LẠI để tránh bị trừ tiền hai lần. Hệ thống đang tự động kiểm tra trạng thái giao dịch với ngân hàng và sẽ cập nhật kết quả trong vòng 5 phút."
+2. Trạng thái cô lập bảo vệ (Isolated State &amp; Idempotency Locking):
+- Hệ thống khóa giao diện thanh toán của đơn hàng (Disable nút 'Thanh toán') và chuyển trạng thái đơn hàng sang 'Đang chờ đối soát cổng thanh toán' (PAYMENT_PENDING_VERIFICATION).
+- Gắn khóa Idempotency Key duy nhất cho đơn hàng này tại backend; mọi yêu cầu thanh toán mới gửi lên với cùng order_id sẽ bị từ chối ngay lập tức.
+3. Phương án phục hồi tự động không tạo khoản trừ tiền hai lần (Recovery Mechanism):
+- Backend kích hoạt tác vụ nền bất đồng bộ (Background Polling / Webhook Listener) để truy vấn trực tiếp trạng thái giao dịch từ cổng thanh toán qua API đối soát (Query Transaction Status API) theo lịch trình backoff (sau 30s, 1m, 3m).
+- Kịch bản 1 (Cổng thanh toán báo Thành công): Tự động cập nhật đơn hàng thành 'Đã thanh toán', gửi email biên lai và thông báo thành công cho người dùng.
+- Kịch bản 2 (Cổng thanh toán báo Thất bại / Chưa nhận được tiền): Sau 5 phút đối soát không thành công, hệ thống mở khóa Idempotency Key, cập nhật trạng thái đơn thành 'Thanh toán gián đoạn', thông báo cho khách hàng là chưa bị trừ tiền và hướng dẫn họ thử lại an toàn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Sự cố mạng là bất khả kháng (Network Partition / Timeout in Distributed Systems). Khi không rõ trạng thái giao dịch, quy tắc sống còn là 'Tuyệt đối không giả định thất bại'. Sử dụng Idempotency Key kết hợp cơ chế Reconcile đối soát bất đồng bộ bảo vệ khách hàng khỏi thảm họa trừ tiền trùng lặp (Double-charging).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Stripe API Documentation - Idempotent Requests (https://stripe.com/docs/api/idempotent_requests); Martin Fowler - Patterns of Distributed Systems.</t>
         </is>
       </c>
     </row>
@@ -898,10 +969,24 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết ba phần: điều kiện hợp lệ, cách nhận biết không hợp lệ và hành vi khi đó.
-Phân tích theo nguyên lý thiết kế: Viết ba phần: điều kiện hợp lệ, cách nhận biết không hợp lệ và hành vi khi đó.</t>
+- Định nghĩa ODD rõ ràng đủ 3 điều kiện (1.0 điểm): Nêu đủ điều kiện ánh sáng, góc chụp 0-30 độ và 3 dòng thiết bị hợp lệ.
+- Bộ phát hiện ngoài phạm vi (1.0 điểm): Đưa ra thuật toán kiểm tra ánh sáng/độ nét và kiểm tra loại thiết bị/góc chụp.
+- Hành vi suy giảm an toàn (1.0 điểm): Từ chối đoán mò, hướng dẫn chụp lại và chuyển tiếp kỹ thuật viên con người khi cần.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Bản đặc tả miền thiết kế vận hành (Operational Design Domain - ODD):
+Hệ thống nhận diện hư hỏng chỉ được bảo đảm hoạt động tin cậy KHI VÀ CHỈ KHI thỏa mãn đồng thời 3 điều kiện môi trường:
+- Điều kiện chiếu sáng: Cường độ ánh sáng môi trường đạt mức chuẩn (độ rọi &gt; 300 lux, không bị chói lóa hay quá tối).
+- Góc chụp: Góc nghiêng của camera so với bề mặt hư hại nằm nghiêm ngặt trong khoảng từ 0 đến 30 độ.
+- Phạm vi thiết bị: Thuộc đúng 3 dòng thiết bị được hỗ trợ trong danh mục huấn luyện chính thức (ví dụ: Model X-100, Y-200, Z-300).
+2. Bộ phát hiện ngoài phạm vi (Out-of-Domain Detector):
+- Bộ kiểm tra chất lượng ảnh (Image Quality Pre-check): Sử dụng thuật toán đo độ sáng histogram/độ sắc nét (Laplacian variance) để phát hiện ảnh thiếu sáng hoặc mờ nhòe.
+- Bộ phân loại góc chụp và loại thiết bị: Kiểm tra góc chụp qua cảm biến góc nghiêng/pose estimation và đối chiếu mã thiết bị/serial qua QR code hoặc OCR nhãn máy. Nếu ngoài 3 dòng máy quy định, kích hoạt cờ OOD (Out-of-Domain Flag).
+3. Hành vi suy giảm có kiểm soát (Graceful Degradation Behavior):
+Khi phát hiện đầu vào nằm ngoài ODD, hệ thống KHÔNG CỐ GẮNG ĐOÁN MÒ hư hỏng mà kích hoạt cơ chế suy giảm an toàn: (1) Từ chối đưa ra kết luận tự động; (2) Hiển thị thông báo hướng dẫn cụ thể trên màn hình ('Ảnh quá tối hoặc góc chụp quá nghiêng &gt;30 độ, vui lòng chụp lại chính diện'); (3) Nếu người dùng không thể chụp lại, cho phép chuyển tiếp toàn bộ ảnh và yêu cầu sang hàng đợi thẩm định của kỹ thuật viên con người.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Khái niệm ODD (Operational Design Domain) xuất phát từ tiêu chuẩn kỹ nghệ an toàn xe tự hành (SAE J3016). Một mô hình AI chỉ có giá trị khi nó tự nhận thức được giới hạn hoạt động an toàn của chính mình. Từ chối xử lý khi điều kiện ngoài tầm kiểm soát và suy giảm có kiểm soát là biểu hiện cao nhất của AI đáng tin cậy.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SAE International Standard J3016 - Operational Design Domain (ODD); ISO 21448 - Safety of the Intended Functionality (SOTIF) (https://www.iso.org/standard/70939.html)</t>
         </is>
       </c>
     </row>
@@ -983,10 +1068,27 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo dõi dữ liệu gốc và dữ liệu dẫn xuất qua từng nơi lưu trữ/đọc.
-Phân tích theo nguyên lý thiết kế: Theo dõi dữ liệu gốc và dữ liệu dẫn xuất qua từng nơi lưu trữ/đọc.</t>
+- Phân định dữ liệu gốc/dẫn xuất và cơ chế khử PII (1.0 điểm): Tách rõ CV gốc khỏi tóm tắt gắn mã CandidateID, nêu cơ chế khử PII trước khi gọi mô hình.
+- Phân quyền và thời hạn lưu giữ 14 ngày (1.0 điểm): Nhân viên chỉ xem tóm tắt, CV gốc lưu kho riêng tự động xóa sau 14 ngày qua lifecycle policy.
+- Định nghĩa các luồng bị cấm tuyệt đối (1.0 điểm): Cấm gửi PII sang LLM công khai hoặc ghi vào nhật ký dùng chung.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế luồng dữ liệu và ranh giới xử lý dữ liệu nhạy cảm cho trợ lý tuyển dụng:
+1. Phân định dữ liệu gốc và dữ liệu dẫn xuất (Raw vs Derived Data):
+- Dữ liệu gốc (Raw CV): Chứa đầy đủ PII (Số điện thoại, email, địa chỉ nhà, họ tên, lịch sử làm việc chi tiết).
+- Dữ liệu dẫn xuất (Derived Summary): Bản tóm tắt kỹ năng, số năm kinh nghiệm và điểm xếp hạng được gắn với mã định danh ngẫu nhiên (CandidateID, ví dụ `CAND-9823`), hoàn toàn không chứa PII.
+2. Ranh giới khử thông tin nhận dạng cá nhân (PII Redaction Boundary):
+- Ngay khi CV được tải lên, một dịch vụ làm sạch PII cục bộ (On-premises PII Masking Service / Microsoft Presidio) tự động bóc tách và thay thế toàn bộ SĐT, địa chỉ, họ tên thành các nhãn ẩn danh `[PHONE]`, `[ADDRESS]`, `[NAME]`.
+- Chỉ có văn bản đã được khử PII mới được truyền vào mô hình ngôn ngữ để tạo bản tóm tắt kỹ năng.
+3. Phân quyền truy cập và thời hạn lưu giữ (Retention &amp; Access Control):
+- Nhân viên tuyển dụng: Chỉ được cấp quyền đọc dữ liệu dẫn xuất (Bản tóm tắt kỹ năng và CandidateID) trên giao diện ATS.
+- CV gốc: Lưu trữ tại vùng lưu trữ riêng biệt (Private S3 Bucket mã hóa KMS với phân quyền IAM nghiêm ngặt). Thiết lập chính sách vòng đời tự động xóa vĩnh viễn (S3 Lifecycle Expiration Policy) đúng sau 14 ngày.
+4. Các luồng dữ liệu bị cấm tuyệt đối (Forbidden Data Flows):
+- CẤM TUYỆT ĐỐI việc gửi CV gốc hoặc văn bản chưa làm sạch PII sang các mô hình công khai đám mây (Public Cloud LLMs) hoặc hệ thống phân tích bên thứ ba.
+- CẤM ghi log chứa SĐT, địa chỉ của ứng viên vào hệ thống nhật ký ứng dụng (Application Logs).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc Giảm thiểu Dữ liệu (Data Minimization) và Ẩn danh hóa (Pseudonymization) theo tiêu chuẩn GDPR và Luật Bảo vệ Dữ liệu Cá nhân. Bằng cách tách biệt vùng lưu trữ dữ liệu gốc có hạn sử dụng (14 ngày) khỏi dữ liệu dẫn xuất phục vụ tuyển dụng, doanh nghiệp triệt tiêu nguy cơ rò rỉ thông tin cá nhân của ứng viên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+GDPR Article 5 - Principles relating to processing of personal data (Data Minimization); Microsoft Presidio - Data Protection and De-identification (https://microsoft.github.io/presidio/)</t>
         </is>
       </c>
     </row>
@@ -1020,10 +1122,26 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đánh dấu dữ liệu gốc ở đâu, ai được xem bản dẫn xuất nào và đường nào phải bị chặn tuyệt đối.
-Phân tích theo nguyên lý thiết kế: Đánh dấu dữ liệu gốc ở đâu, ai được xem bản dẫn xuất nào và đường nào phải bị chặn tuyệt đối.</t>
+- Chỉ ra đủ 4 vi phạm nghiêm trọng (1.5 điểm): Nêu đúng lộ log dùng chung, gửi LLM công khai, kỹ sư thấy data gốc và thiếu cơ chế xóa 30 ngày.
+- Thiết kế lại đường đi dữ liệu an toàn (1.5 điểm): Nêu rõ bước khử PII/Tokenization, chặn mô hình công khai, chỉ lưu log ẩn danh có TTL 30 ngày.
+- Phân quyền xem của kỹ sư và bước kiểm toán (1.0 điểm): Kỹ sư chỉ xem metrics tổng hợp; có cron job kiểm toán xóa dữ liệu định kỳ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Bốn vi phạm nghiêm trọng trong luồng đề xuất ban đầu:
+- Vi phạm 1: Ghi dữ liệu giao dịch gốc (chứa số tài khoản, số dư, tên khách hàng) vào nhật ký dùng chung (Shared Logs), vi phạm nghiêm trọng tính bảo mật và phân quyền.
+- Vi phạm 2: Gửi dữ liệu giao dịch gốc sang mô hình công khai (Public LLM), vi phạm quy định bí mật ngân hàng và nguy cơ rò rỉ dữ liệu tài chính ra bên ngoài.
+- Vi phạm 3: Cho phép kỹ sư xem dữ liệu giao dịch gốc qua bảng điều khiển, vi phạm nguyên tắc 'Kỹ sư không được xem dữ liệu giao dịch gốc'.
+- Vi phạm 4: Nhật ký đề xuất không có cơ chế tự động hủy sau 30 ngày, vi phạm ràng buộc lưu giữ tối đa 30 ngày.
+2. Viết lại đường đi dữ liệu chuẩn mực và an toàn (Redesigned Architecture):
+- Bước 1: [Dữ liệu giao dịch gốc] nằm trong vùng mạng bảo mật Core Banking (Secure PCI-DSS Zone).
+- Bước 2: Một dịch vụ khử PII / Tokenizer nội bộ (Tokenization Service) bóc tách toàn bộ thông tin nhạy cảm, thay thế số tài khoản bằng mã băm giả lập (Pseudonymized Token) và chỉ giữ lại loại giao dịch/mã lỗi.
+- Bước 3: Chỉ truyền bản dữ liệu đã khử PII vào mô hình ngân hàng riêng biệt (Private LLM / On-premises Model), TUYỆT ĐỐI CHẶN đường truyền tới mô hình công khai.
+- Bước 4: Nhật ký chỉ lưu trữ các chỉ số ẩn danh và mã trace (không lưu PII), được cấu hình chính sách TTL (Time-To-Live) tự động xóa sau 30 ngày.
+3. Phần dữ liệu kỹ sư được phép xem: Kỹ sư chỉ được xem Bảng điều khiển vi sai (Aggregated Telemetry Dashboard) gồm: tỷ lệ lỗi, mã phản hồi HTTP, độ trễ và số token tiêu thụ, hoàn toàn không có dữ liệu giao dịch cụ thể.
+4. Bước xóa và kiểm toán định kỳ: Hệ thống kích hoạt Cron Job kiểm toán hàng ngày để kiểm tra chính sách xóa sạch dữ liệu nhật ký quá 30 ngày, ghi nhận biên bản kiểm toán kiểm tra tuân thủ an ninh thông tin.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tiêu chuẩn an ninh ngành ngân hàng (PCI-DSS &amp; Banking Secrecy Regulations) nghiêm cấm việc đưa dữ liệu tài chính khách hàng vào các hệ thống dùng chung hay mô hình AI của bên thứ ba. Thiết kế hệ thống AI tài chính phải tuân thủ triệt để nguyên tắc Zero Trust và Data Tokenization tại biên mạng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+PCI-DSS v4.0 - Requirement 3: Protect Stored Account Data (https://www.pcisecuritystandards.org/); NIST SP 800-88 Rev. 1 - Guidelines for Media Sanitization.</t>
         </is>
       </c>
     </row>
@@ -1058,10 +1176,27 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết đủ năm phần: ai hưởng lợi, chỉ số, ngưỡng, thời gian và hành động.
-Phân tích theo nguyên lý thiết kế: Viết đủ năm phần: ai hưởng lợi, chỉ số, ngưỡng, thời gian và hành động.</t>
+- Đủ chỉ số đo, ngưỡng và cửa sổ thời gian (1.5 điểm): Nêu rõ chỉ số FCR (ngưỡng &gt;=75%), độ chính xác trích dẫn (&gt;=95%) và cửa sổ 30 ngày.
+- Hành động quyết định và lỗi có hại cần chặn (1.5 điểm): Nêu rõ hành động mở rộng/dừng sửa, và chỉ số guardrail chống ảo giác nghiêm trọng (&lt;0,5%) có cơ chế ngắt mạch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Viết lại phát biểu chưa đủ ('AI trả lời tốt hơn') thành bộ tiêu chí thành công 5 thành phần chuẩn mực:
+1. Chỉ số đo lường (Measurement Metric):
+- Chỉ số giá trị chính: Tỷ lệ giải quyết yêu cầu thành công ngay trong lượt tương tác đầu tiên (First Contact Resolution - FCR Rate) được người dùng xác nhận.
+- Chỉ số chất lượng kỹ thuật: Tỷ lệ câu trả lời có trích dẫn đúng tài liệu chính sách nội bộ (Grounded Citation Precision).
+2. Ngưỡng thành công (Target Threshold):
+- FCR đạt tối thiểu 75% (so với mốc nền thủ công hiện tại là 55%).
+- Grounded Citation Precision đạt tối thiểu 95%.
+3. Cửa sổ đo lường (Measurement Window):
+Đo lường liên tục trong vòng 30 ngày thử nghiệm Pilot trên tập mẫu tối thiểu 2.000 yêu cầu thực tế của khách hàng.
+4. Hành động tương ứng khi đạt / không đạt (Action Trigger):
+- Nếu đạt ngưỡng: Chính thức mở rộng triển khai cho 100% người dùng trên toàn hệ thống.
+- Nếu không đạt ngưỡng: Dừng mở rộng, kích hoạt phân tích 100 ca thất bại gần nhất để tinh chỉnh RAG và quy tắc định tuyến.
+5. Lỗi có hại cần chặn đứng (Guardrail / Harmful Failure Metric):
+Tỷ lệ ảo giác thông tin gây sai lệch chính sách nghiêm trọng (Critical Policy Hallucination Rate) phải được giữ nghiêm ngặt ở mức &lt; 0,5%; nếu vượt quá 1%, lập tức ngắt hệ thống AI tự động (Circuit Breaker) và chuyển toàn bộ cuộc gọi/chat về cho nhân viên con người.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Một tiêu chí thành công sản phẩm AI (AI Success Criteria) bắt buộc phải cụ thể hóa thành hợp đồng đo lường 5 phần (Metric, Threshold, Window, Action, Guardrail). Tránh các phát biểu định tính cảm tính ('tốt hơn', 'thông minh hơn') vốn không thể nghiệm thu hay kiểm toán trong kỹ nghệ phần mềm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Success Metrics &amp; Guardrails (https://pair.withgoogle.com/guidebook/); Doerr, J. (2018). Measure What Matters.</t>
         </is>
       </c>
     </row>
@@ -1093,10 +1228,27 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một chỉ số trả lời “tốt cho ai”, chỉ số kia trả lời “lỗi nào không thể chấp nhận”.
-Phân tích theo nguyên lý thiết kế: Một chỉ số trả lời “tốt cho ai”, chỉ số kia trả lời “lỗi nào không thể chấp nhận”.</t>
+- Tiêu chí đo giá trị học viên thực chất (1.5 điểm): Nêu chỉ số tỷ lệ hoàn thành bài thực hành sau gợi ý (&gt;=65%), phân tích vượt trội hơn CTR.
+- Rào chắn an toàn định lượng (1.5 điểm): Thiết lập guardrail chống lệch kiến thức tiên quyết (&lt;2%).
+- Hành động ngắt mạch khi vi phạm guardrail (1.0 điểm): Chuyển sang lộ trình học tĩnh của giảng viên và cảnh báo đội ngũ kỹ thuật.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế bộ tiêu chí thành công và rào chắn cho hệ thống gợi ý tài liệu học tập:
+1. Tiêu chí đo lường giá trị thực tế cho học viên (Value Metric):
+- Chỉ số: Tỷ lệ hoàn thành bài tập thực hành thành công trong vòng 24 giờ sau khi nhấp vào tài liệu gợi ý (Post-Recommendation Assignment Completion Rate).
+- Ngưỡng mục tiêu: Đạt tối thiểu 65% (tăng 25% so với nhóm không sử dụng hệ thống gợi ý trong thử nghiệm A/B).
+- Ý nghĩa: Đo lường giá trị học tập thực chất (học viên hiểu bài và làm được bài), thay vì chỉ đo tỷ lệ nhấp chuột bề mặt (Click-Through Rate - CTR vốn dễ bị thao túng bởi mồi nhử giật gân).
+2. Rào chắn an toàn chống gợi ý sai lệch (Guardrail Metric):
+- Chỉ số Guardrail: Tỷ lệ gợi ý tài liệu vượt quá trình độ tiên quyết (Prerequisite Mismatch Rate) hoặc tài liệu có nội dung lỗi thời/chưa được kiểm duyệt.
+- Ngưỡng tối đa cho phép: Nghiêm ngặt ở mức &lt; 2% trên tổng số lượt gợi ý được hiển thị.
+- Ý nghĩa: Ngăn chặn việc hệ thống gợi ý bài giảng quá nâng cao gây nản lòng cho học viên mới bắt đầu, hoặc gợi ý tài liệu sai lệch kiến thức chuyên môn.
+3. Hành vi của hệ thống khi Guardrail không đạt (Action on Guardrail Breach):
+- Kích hoạt chế độ suy giảm an toàn (Fallback to Curated Content): Ngay khi chỉ số Prerequisite Mismatch Rate vượt quá ngưỡng 2% trong khung thời gian 24 giờ, thuật toán AI tự động bị đình chỉ quyền gợi ý động.
+- Hệ thống chuyển ngay sang hiển thị lộ trình học tập tĩnh chuẩn hóa do giảng viên biên soạn trước (Fixed Curriculum Roadmap).
+- Tự động gửi cảnh báo khẩn cấp (PagerDuty/Slack alert) cho Quản lý Sản phẩm và Kỹ sư ML phụ trách để kiểm tra lỗi trôi dạt phân phối dữ liệu (Data Drift).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Thiết kế hệ thống gợi ý học tập (Educational Recommendation System) phải đặt 'Kết quả học tập' (Learning Outcome) làm North Star Metric, đối trọng với 'Rào chắn kiến thức tiên quyết' (Prerequisite Guardrail). Tối ưu hóa CTR mà không có guardrail sẽ biến hệ thống thành một cỗ máy câu view gây hại cho tiến trình học tập của học viên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anderson, J. R., et al. (1995). Cognitive Tutors: Lessons Learned. The Journal of the Learning Sciences; Google Responsible AI Practices - Recommender Systems (https://ai.google/responsibility/principles/)</t>
         </is>
       </c>
     </row>
@@ -1131,10 +1283,19 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính hai mẫu số khác nhau rồi so hậu quả của FP và FN.
-Phân tích theo nguyên lý thiết kế: Tính hai mẫu số khác nhau rồi so hậu quả của FP và FN.</t>
+- Tính chính xác Precision và Recall (1.5 điểm): Tính đúng Precision = 90.0% (72/80) và Recall = 80.0% (72/90).
+- Đề xuất hướng vận hành dựa trên hậu quả (1.5 điểm): Phân tích tác hại nặng của FP, đề xuất nâng ngưỡng tự tin để tối ưu hóa Precision và chuyển FN cho con người hỗ trợ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Precision và Recall theo số liệu ma trận nhầm lẫn ($TP=72, FP=8, FN=18$):
+- Độ chính xác (Precision): $\text{Precision} = \frac{TP}{TP + FP} = \frac{72}{72 + 8} = \frac{72}{80} = 0.900$ (90,0%).
+- Độ bao phủ (Recall): $\text{Recall} = \frac{TP}{TP + FN} = \frac{72}{72 + 18} = \frac{72}{90} = 0.800$ (80,0%).
+2. Đề xuất hướng vận hành sản phẩm (Product Operational Strategy):
+- Phân tích hậu quả: False Positive (FP) có hậu quả cực kỳ nghiêm trọng (gửi lời khuyên sai lầm trực tiếp cho người dùng, phá hủy niềm tin thương hiệu và rủi ro pháp lý). Trong khi đó, False Negative (FN) chỉ gây bất tiện nhẹ (chậm trễ hỗ trợ tạm thời nhưng khách hàng vẫn được chuyển cho nhân viên xử lý tiếp theo).
+- Chiến lược vận hành: Bắt buộc phải ưu tiên TỐI ĐA HÓA PRECISION (High Precision Strategy). Cần nâng ngưỡng quyết định của mô hình (Classification Decision Threshold, ví dụ từ 0,5 lên 0,85). Chỉ cho phép hệ thống tự động đưa ra lời khuyên khi mô hình đạt độ tin cậy tuyệt đối (đẩy FP về sát 0); chấp nhận Recall giảm xuống (FN tăng lên), và toàn bộ các trường hợp mô hình không chắc chắn sẽ được chuyển tiếp an toàn cho tư vấn viên con người thẩm định.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Sự đánh đổi Precision-Recall (Precision-Recall Trade-off) trong sản phẩm AI luôn được định đoạt bởi Ma trận Chi phí Bất cân xứng (Asymmetric Cost Matrix). Khi chi phí của lỗi FP (gửi lời khuyên sai nguy hại) lớn gấp nhiều lần chi phí của FN (chờ đợi), sản phẩm bắt buộc phải hy sinh độ bao phủ (Recall) để bảo vệ tuyệt đối độ tin cậy (Precision).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Provost, F., &amp; Fawcett, T. (2013). Data Science for Business: What You Need to Know about Data Mining and Data-Analytic Thinking. O'Reilly Media; Google Machine Learning Crash Course - Precision and Recall (https://developers.google.com/machine-learning/crash-course/classification/precision-and-recall)</t>
         </is>
       </c>
     </row>
@@ -1267,10 +1428,29 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ưu tiên rủi ro thảm họa, rồi đánh dấu ước tính yếu cần kiểm chứng.
-Phân tích theo nguyên lý thiết kế: Ưu tiên rủi ro thảm họa, rồi đánh dấu ước tính yếu cần kiểm chứng.</t>
+- Thứ tự ưu tiên chuẩn xác (1.0 điểm): Xếp đúng R2 (ưu tiên 1 - thảm họa), R3 (ưu tiên 2 - thiếu bằng chứng), R1 (ưu tiên 3 - rủi ro thấp/log rõ).
+- Người phụ trách tương ứng (1.0 điểm): Gán đúng CISO/Security cho R2, SRE cho R3 và PM cho R1.
+- Bước xác minh và kiểm chứng kỹ thuật (1.0 điểm): Nêu rõ Pen-test cho R2, Load test cho R3 và cải tiến UI chuyển tuyến cho R1.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Xếp hạng ưu tiên xử lý rủi ro và phương án xác minh:
+1. Thứ tự ưu tiên xử lý: R2 -&gt; R3 -&gt; R1.
+2. Phân tích chi tiết từng rủi ro, người phụ trách và bước kiểm chứng:
+- Ưu tiên 1: R2 (Lộ dữ liệu cá nhân - Xác suất 0,1%, Mức độ thảm họa / Cực cao)
+  + Lý do: Nguyên tắc an toàn hệ thống quy định các rủi ro thảm họa đe dọa sự tồn vong của doanh nghiệp (phạt hàng triệu USD, đình chỉ hoạt động) phải luôn được đặt ở mức ưu tiên tuyệt đối, bất kể xác suất lý thuyết nhỏ. Hơn nữa, con số 0,1% chỉ là 'ước tính' chưa có kiểm chứng thực tế.
+  + Người phụ trách: Trưởng phòng An toàn Thông tin (CISO / Security Lead).
+  + Bước kiểm chứng: Thực hiện kiểm thử thâm nhập (Penetration Testing) và rà quét lỗ hổng rò rỉ dữ liệu (DLP) ngay lập tức.
+- Ưu tiên 2: R3 (Hết thời gian chờ - Xác suất 2%, Mức độ vừa, ước tính từ 10 ca)
+  + Lý do: Cỡ mẫu 10 trường hợp là quá nhỏ, độ không chắc chắn cao. Cần kiểm tra để tránh rủi ro hệ thống bị treo lan truyền.
+  + Người phụ trách: Kỹ sư Hạ tầng / SRE Lead.
+  + Bước kiểm chứng: Thực hiện kiểm thử tải (Load Testing / Stress Testing) với 500 yêu cầu đồng thời để đo tỷ lệ timeout thực tế.
+- Ưu tiên 3: R1 (Chuyển nhầm tuyến - Xác suất 5%, Mức độ thấp, có log 3 tháng)
+  + Lý do: Bằng chứng rất tin cậy (log 3 tháng), mức độ nghiêm trọng thấp (chỉ là chuyển nhầm tuyến có thể sửa).
+  + Người phụ trách: Quản lý Sản phẩm (Product Manager).
+  + Bước kiểm chứng: Thêm nút bấm chuyển lại tuyến nhanh và tinh chỉnh bảng từ khóa định tuyến.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong ma trận rủi ro (Risk Matrix), Điểm rủi ro = Xác suất × Mức độ nghiêm trọng. Tuy nhiên, đối với rủi ro đuôi béo (Fat-tailed / Catastrophic Risk) như rò rỉ dữ liệu, mức độ nghiêm trọng tiệm cận vô cùng nên bắt buộc phải xử lý trước. Đồng thời, các rủi ro có độ tin cậy bằng chứng yếu (ước tính 10 ca) phải được đưa vào kiểm thử xác minh khẩn cấp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST SP 800-30 Rev. 1 - Guide for Conducting Risk Assessments (https://csrc.nist.gov/publications/detail/sp/800-30/rev-1/final); Taleb, N. N. (2007). The Black Swan: The Impact of the Highly Improbable.</t>
         </is>
       </c>
     </row>
@@ -1352,10 +1532,26 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi mệnh đề trong mô tả phải xuất hiện thành trường hợp, chỉ số hoặc phép kiểm soát.
-Phân tích theo nguyên lý thiết kế: Mỗi mệnh đề trong mô tả phải xuất hiện thành trường hợp, chỉ số hoặc phép kiểm soát.</t>
+- Bộ test case đại diện và ca biên/tài chính (1.5 điểm): Liệt kê đủ ca chuẩn, ca biên mâu thuẫn chính sách và ca ranh giới tài chính.
+- Chỉ số đo lường và ngưỡng chấp thuận rõ ràng (1.5 điểm): Nêu rõ chỉ số thời gian xử lý (&lt;=4 phút vs mốc nền 14 phút), độ chính xác trích dẫn (&gt;=98%) và tuân thủ ranh giới tài chính (100%).
+- Các phép kiểm soát hệ thống tương ứng (1.0 điểm): Thiết kế bộ kiểm tra trích dẫn tự động và cổng chặn phê duyệt tài chính trước khi phát hành.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Kế hoạch Đánh giá (Eval Plan) toàn diện dựa trên mô tả bài toán và các ranh giới nghiệp vụ:
+1. Tập trường hợp kiểm thử đại diện và ca biên (Evaluation Dataset):
+- Ca đại diện (Standard Happy Path): 100 câu hỏi về các chính sách nhân sự, ngày phép phổ biến được quy định rõ trong tài liệu có sẵn.
+- Ca biên (Edge Cases): 30 câu hỏi về các điều khoản có ngoại lệ hoặc phiên bản thay đổi gần đây; 20 câu hỏi có nội dung mâu thuẫn giữa các tài liệu.
+- Ca ranh giới tài chính (Financial Boundary Cases): 30 yêu cầu liên quan đến hoàn tiền, thanh toán công tác phí hoặc hỗ trợ tài chính để kiểm tra cơ chế bắt buộc phê duyệt của con người.
+2. Chỉ số đo lường và ngưỡng chấp thuận (Metrics &amp; Thresholds):
+- Thời gian xử lý trung vị của nhân viên (Median Handling Time): Đạt &lt;= 4 phút (giảm vượt bậc so với mốc nền thủ công 14 phút).
+- Độ chính xác trích dẫn nguồn (Grounded Citation Precision): Đạt &gt;= 98% (mọi bản nháp bắt buộc phải có trích dẫn đúng số điều khoản và URL tài liệu gốc).
+- Tỷ lệ an toàn ranh giới tài chính (Financial Gating Compliance): Đạt tuyệt đối 100% (không có bất kỳ yêu cầu tài chính nào được tự động phát đi mà thiếu chữ ký phê duyệt của con người).
+3. Các phép kiểm soát hệ thống (Control Mechanisms):
+- Bộ kiểm tra trích dẫn tự động (Automated Citation Verifier): So khớp trích dẫn với tài liệu chính sách, nếu không tìm thấy trích dẫn hợp lệ thì khóa không cho hiển thị bản nháp.
+- Cổng chặn phê duyệt tài chính (Financial Approval Gate): Bộ lọc regex/classifier phát hiện ý định tài chính và tự động chuyển giao diện sang luồng ký duyệt của người có thẩm quyền.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Kế hoạch đánh giá (Eval Plan) là cầu nối giữa Bài toán nghiệp vụ (Problem Statement) và Hệ thống kiểm thử tự động (Evaluation Harness). Mỗi ràng buộc trong bản mô tả bài toán (14 phút, trích dẫn, phê duyệt tài chính) đều phải được chuyển hóa thành các trường hợp kiểm thử định lượng và chốt chặn kiểm soát tương ứng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Service Level Objectives and Error Budgets (https://sre.google/sre-book/service-level-objectives/); LangChain Evaluation Guide (https://python.langchain.com/docs/concepts/evaluation/)</t>
         </is>
       </c>
     </row>
